--- a/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
+++ b/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
@@ -211,12 +211,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$A$3:$A$109</f>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$149</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$B$2:$B$109</f>
+              <f>'Ημερήσια Πρόοδος'!$B$2:$B$149</f>
             </numRef>
           </val>
         </ser>
@@ -331,12 +331,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$A$3:$A$109</f>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$149</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$C$2:$C$109</f>
+              <f>'Ημερήσια Πρόοδος'!$C$2:$C$149</f>
             </numRef>
           </val>
         </ser>
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2167,10 +2167,530 @@
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>334</v>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>16/08</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>17/08</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>18/08</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>19/08</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>20/08</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>22/08</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>23/08</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>24/08</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>25/08</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>28/08</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>29/08</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>30/08</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>31/08</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>01/09</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>02/09</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>03/09</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>05/09</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>06/09</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>07/09</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>08/09</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>09/09</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>11/09</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>12/09</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>13/09</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>14/09</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>15/09</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>16/09</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>17/09</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>19/09</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>20/09</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>21/09</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>22/09</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>23/09</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>24/09</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>1969</v>
       </c>
     </row>
   </sheetData>
@@ -2185,7 +2705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2292,65 +2812,86 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>123</v>
+        <v>1273</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>01/08</t>
+          <t>25/08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Σεπτέμβριος 2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>485</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>02/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Μόνιμες / ζωντανές πηγές</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B7" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>ΣΥΝΟΛΟ</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>334</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B8" s="5" t="n">
+        <v>1969</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
+++ b/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
@@ -211,12 +211,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$A$3:$A$149</f>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$181</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$B$2:$B$149</f>
+              <f>'Ημερήσια Πρόοδος'!$B$2:$B$181</f>
             </numRef>
           </val>
         </ser>
@@ -331,12 +331,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$A$3:$A$149</f>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$181</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$C$2:$C$149</f>
+              <f>'Ημερήσια Πρόοδος'!$C$2:$C$181</f>
             </numRef>
           </val>
         </ser>
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2687,10 +2687,426 @@
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C149" s="3" t="n">
-        <v>1969</v>
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>25/09</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>26/09</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>27/09</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>28/09</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>29/09</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>30/09</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>01/10</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>02/10</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>03/10</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>05/10</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>06/10</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>07/10</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>08/10</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>09/10</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>11/10</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>12/10</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>13/10</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>14/10</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>15/10</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>16/10</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>17/10</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>18/10</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>19/10</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>20/10</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>21/10</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>22/10</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>23/10</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>1970</v>
       </c>
     </row>
   </sheetData>
@@ -2833,10 +3249,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>93</v>
@@ -2879,7 +3295,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
